--- a/schedule_output.xlsx
+++ b/schedule_output.xlsx
@@ -39965,10 +39965,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -39987,10 +39987,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">

--- a/schedule_output.xlsx
+++ b/schedule_output.xlsx
@@ -39877,15 +39877,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39926,6 +39927,11 @@
           <t>Single-Room Days</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
@@ -39948,6 +39954,11 @@
       <c r="F3" s="17" t="n">
         <v>50</v>
       </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>Column generation optimal — all 3 constraints enforced</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
@@ -39970,6 +39981,11 @@
       <c r="F4" s="15" t="n">
         <v>50</v>
       </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>H_{d,p} restricted to single-room patterns via CG feasibility constraint</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -39992,6 +40008,11 @@
       <c r="F5" s="13" t="n">
         <v>50</v>
       </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Same as day variant with post-processing to enforce consistent weekly room</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -40014,6 +40035,11 @@
       <c r="F6" s="15" t="n">
         <v>50</v>
       </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>K_{d,p} restricted to rooms within 3m of anchor — C_p constraint</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -40036,6 +40062,11 @@
       <c r="F7" s="13" t="n">
         <v>50</v>
       </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>K_{d,p} restricted to rooms within 5m of anchor — C_p constraint</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
@@ -40058,21 +40089,26 @@
       <c r="F8" s="15" t="n">
         <v>49</v>
       </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>x_{ird} ≤ a_{id}: HPW114 unavailable on 11-11-2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>D – Admin Overflow ON</t>
+          <t>D – Admin Buffer ON (B=30min)</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>36.5</v>
+        <v>25.2</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.57</v>
+        <v>0.39</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>64</v>
@@ -40080,21 +40116,26 @@
       <c r="F9" s="13" t="n">
         <v>50</v>
       </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>MP Constraint (4): Σ τ_i · α ≤ B_d=30min per day</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>D – Admin Overflow OFF</t>
+          <t>D – Admin Buffer OFF</t>
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>35.5</v>
+        <v>25.2</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.55</v>
+        <v>0.39</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>64</v>
@@ -40102,6 +40143,11 @@
       <c r="F10" s="15" t="n">
         <v>50</v>
       </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Hard block: admin-window appointments excluded from pattern generator</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -40124,32 +40170,69 @@
       <c r="F11" s="13" t="n">
         <v>50</v>
       </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Σ x_{ird} ≤ capacity_r + δ_r: no-shows included in schedule</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>F – Uncertainty σ=20%</t>
+          <t>F – Buffer Factor μ=20%</t>
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>36.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.57</v>
+        <v>1.43</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>50</v>
+        <v>16</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>d'_i = d_i(1+μ): buffered durations in preprocessing and CG only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>F – Buffer Factor μ=10%</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>162</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>d'_i = d_i(1+μ): less conservative buffer for comparison</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
